--- a/组合实盘追踪/20260518_银河.xlsx
+++ b/组合实盘追踪/20260518_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>694.6</v>
+        <v>701.8</v>
       </c>
       <c r="D2" s="1">
-        <v>-3</v>
+        <v>4.2</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0043</v>
+        <v>0.006</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-16.5</v>
+        <v>-9.3</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0232</v>
+        <v>-0.0131</v>
       </c>
       <c r="L2" s="1">
-        <v>-16.5</v>
+        <v>-9.3</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0232</v>
+        <v>-0.0131</v>
       </c>
       <c r="N2" s="1">
-        <v>-6.6</v>
+        <v>1.4</v>
       </c>
       <c r="O2" s="1">
-        <v>-16.5</v>
+        <v>-9.5</v>
       </c>
       <c r="P2" s="1">
-        <v>-16.5</v>
+        <v>-9.5</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0237</v>
+        <v>0.0238</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>6</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0043</v>
+        <v>0.006</v>
       </c>
       <c r="U2" s="5">
-        <v>3.473</v>
+        <v>3.509</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0239</v>
+        <v>0.0134</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0429</v>
+        <v>0.0537</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0572</v>
+        <v>0.0682</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1559</v>
+        <v>0.1679</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4459</v>
+        <v>0.4608</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>830.4</v>
+        <v>839.6</v>
       </c>
       <c r="D3" s="1">
-        <v>-5.2</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0062</v>
+        <v>0.0048</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-32.5</v>
+        <v>-23.3</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0377</v>
+        <v>-0.027</v>
       </c>
       <c r="L3" s="1">
-        <v>-32.5</v>
+        <v>-23.3</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0377</v>
+        <v>-0.027</v>
       </c>
       <c r="N3" s="1">
-        <v>-13.6</v>
+        <v>-4</v>
       </c>
       <c r="O3" s="1">
-        <v>-32.5</v>
+        <v>-23.3</v>
       </c>
       <c r="P3" s="1">
-        <v>-32.5</v>
+        <v>-23.3</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0283</v>
+        <v>0.0285</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>6</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0062</v>
+        <v>0.0048</v>
       </c>
       <c r="U3" s="5">
-        <v>2.076</v>
+        <v>2.099</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.039</v>
+        <v>0.0276</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0086</v>
+        <v>0.0024</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.038</v>
+        <v>0.0495</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0549</v>
+        <v>0.0666</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0898</v>
+        <v>0.1018</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>707.3</v>
+        <v>702.9</v>
       </c>
       <c r="D4" s="1">
-        <v>-6.6</v>
+        <v>-11</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.0092</v>
+        <v>-0.0154</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-29.8</v>
+        <v>-34.2</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0404</v>
+        <v>-0.0464</v>
       </c>
       <c r="L4" s="1">
-        <v>-29.8</v>
+        <v>-34.2</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0404</v>
+        <v>-0.0464</v>
       </c>
       <c r="N4" s="1">
-        <v>-13.2</v>
+        <v>-17.6</v>
       </c>
       <c r="O4" s="1">
-        <v>-29.8</v>
+        <v>-32</v>
       </c>
       <c r="P4" s="1">
-        <v>-29.8</v>
+        <v>-32</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0241</v>
+        <v>0.0238</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>6</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.0092</v>
+        <v>-0.0154</v>
       </c>
       <c r="U4" s="5">
-        <v>0.643</v>
+        <v>0.639</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.042</v>
+        <v>0.0485</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0287</v>
+        <v>-0.0347</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.1107</v>
+        <v>-0.1162</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1902</v>
+        <v>-0.1952</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1204</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="D5" s="1">
-        <v>-4.6</v>
+        <v>-1.6</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0047</v>
+        <v>-0.0016</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-20.3</v>
+        <v>-17.3</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0205</v>
+        <v>-0.0175</v>
       </c>
       <c r="L5" s="1">
-        <v>-20.3</v>
+        <v>-17.3</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0205</v>
+        <v>-0.0175</v>
       </c>
       <c r="N5" s="1">
-        <v>-8.4</v>
+        <v>-5.4</v>
       </c>
       <c r="O5" s="1">
-        <v>-20.3</v>
+        <v>-17.5</v>
       </c>
       <c r="P5" s="1">
-        <v>-20.3</v>
+        <v>-17.5</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0331</v>
+        <v>0.033</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>6</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0047</v>
+        <v>-0.0016</v>
       </c>
       <c r="U5" s="5">
-        <v>4.855</v>
+        <v>4.87</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.021</v>
+        <v>0.0179</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0244</v>
+        <v>0.0276</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0394</v>
+        <v>0.0426</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0576</v>
+        <v>0.0609</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.277</v>
+        <v>0.2809</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>944</v>
+        <v>950.7</v>
       </c>
       <c r="D6" s="1">
-        <v>-11.4</v>
+        <v>-4.7</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.0119</v>
+        <v>-0.0049</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-29.7</v>
+        <v>-23</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0305</v>
+        <v>-0.0236</v>
       </c>
       <c r="L6" s="1">
-        <v>-29.7</v>
+        <v>-23</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0305</v>
+        <v>-0.0236</v>
       </c>
       <c r="N6" s="1">
-        <v>-19.8</v>
+        <v>-12.9</v>
       </c>
       <c r="O6" s="1">
-        <v>-29.7</v>
+        <v>-23</v>
       </c>
       <c r="P6" s="1">
-        <v>-29.7</v>
+        <v>-23</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0322</v>
@@ -915,28 +915,28 @@
         <v>6</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0119</v>
+        <v>-0.0049</v>
       </c>
       <c r="U6" s="5">
-        <v>9.44</v>
+        <v>9.507</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0315</v>
+        <v>0.0242</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0588</v>
+        <v>-0.0521</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1073</v>
+        <v>-0.1009</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0629</v>
+        <v>0.0704</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3153</v>
+        <v>0.3247</v>
       </c>
     </row>
     <row r="7">
@@ -947,13 +947,13 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3021.3</v>
+        <v>3015.9</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>-5.4</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>-0.0018</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -968,28 +968,28 @@
         <v/>
       </c>
       <c r="J7" s="1">
-        <v>2.55</v>
+        <v>-2.85</v>
       </c>
       <c r="K7" s="2">
-        <v>0.0008</v>
+        <v>-0.0009</v>
       </c>
       <c r="L7" s="1">
-        <v>2.55</v>
+        <v>-2.85</v>
       </c>
       <c r="M7" s="2">
-        <v>0.0008</v>
+        <v>-0.0009</v>
       </c>
       <c r="N7" s="1">
-        <v>2.7</v>
+        <v>-2.7</v>
       </c>
       <c r="O7" s="1">
-        <v>2.55</v>
+        <v>-2.85</v>
       </c>
       <c r="P7" s="1">
-        <v>2.55</v>
+        <v>-2.85</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1029</v>
+        <v>0.1023</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -998,28 +998,28 @@
         <v>6</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>-0.0018</v>
       </c>
       <c r="U7" s="5">
-        <v>1.119</v>
+        <v>1.117</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
       </c>
       <c r="W7" s="2">
-        <v/>
+        <v>0.0009</v>
       </c>
       <c r="X7" s="2">
-        <v>0.0018</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0081</v>
+        <v>0.0063</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0127</v>
+        <v>0.0109</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0216</v>
+        <v>0.0198</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>782.4</v>
+        <v>791.8</v>
       </c>
       <c r="D8" s="1">
-        <v>-11.6</v>
+        <v>-2.2</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0146</v>
+        <v>-0.0028</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>-4.3</v>
+        <v>5.1</v>
       </c>
       <c r="K8" s="2">
-        <v>-0.0055</v>
+        <v>0.0065</v>
       </c>
       <c r="L8" s="1">
-        <v>-4.3</v>
+        <v>5.1</v>
       </c>
       <c r="M8" s="2">
-        <v>-0.0055</v>
+        <v>0.0065</v>
       </c>
       <c r="N8" s="1">
-        <v>-2.4</v>
+        <v>7</v>
       </c>
       <c r="O8" s="1">
-        <v>-4.3</v>
+        <v>3.5</v>
       </c>
       <c r="P8" s="1">
-        <v>-4.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0267</v>
+        <v>0.0269</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,28 +1081,28 @@
         <v>6</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0146</v>
+        <v>-0.0028</v>
       </c>
       <c r="U8" s="5">
-        <v>3.912</v>
+        <v>3.959</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
       </c>
       <c r="W8" s="2">
-        <v>0.0056</v>
+        <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.0659</v>
+        <v>0.0787</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.1981</v>
+        <v>0.2125</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2685</v>
+        <v>0.2837</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9482</v>
+        <v>0.9716</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19754</v>
+        <v>19852</v>
       </c>
       <c r="D9" s="1">
-        <v>-14</v>
+        <v>84</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0007</v>
+        <v>0.0042</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-623.64</v>
+        <v>-525.64</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0306</v>
+        <v>-0.0258</v>
       </c>
       <c r="L9" s="1">
-        <v>-623.64</v>
+        <v>-525.64</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0306</v>
+        <v>-0.0258</v>
       </c>
       <c r="N9" s="1">
-        <v>-107.8</v>
+        <v>-15.4</v>
       </c>
       <c r="O9" s="1">
-        <v>-623.64</v>
+        <v>-531.24</v>
       </c>
       <c r="P9" s="1">
-        <v>-623.64</v>
+        <v>-531.24</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6729</v>
+        <v>0.6732</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>6</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0007</v>
+        <v>0.0042</v>
       </c>
       <c r="U9" s="5">
-        <v>14.11</v>
+        <v>14.18</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0315</v>
+        <v>0.0264</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.016</v>
+        <v>-0.0111</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0348</v>
+        <v>-0.03</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0334</v>
+        <v>0.0385</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1767</v>
+        <v>0.1825</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>670</v>
+        <v>672.8</v>
       </c>
       <c r="D10" s="1">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0158</v>
+        <v>0.02</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,25 +1217,25 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-2.1</v>
+        <v>0.7</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0031</v>
+        <v>0.001</v>
       </c>
       <c r="L10" s="1">
-        <v>-2.1</v>
+        <v>0.7</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0031</v>
+        <v>0.001</v>
       </c>
       <c r="N10" s="1">
-        <v>6.4</v>
+        <v>8.8</v>
       </c>
       <c r="O10" s="1">
-        <v>-2.1</v>
+        <v>0.3</v>
       </c>
       <c r="P10" s="1">
-        <v>-2.1</v>
+        <v>0.3</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0228</v>
@@ -1247,28 +1247,28 @@
         <v>6</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0158</v>
+        <v>0.02</v>
       </c>
       <c r="U10" s="5">
-        <v>1.675</v>
+        <v>1.682</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.003</v>
+        <v/>
       </c>
       <c r="X10" s="2">
-        <v>0.0091</v>
+        <v>0.0133</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.3199</v>
+        <v>0.3254</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3843</v>
+        <v>0.3901</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2767</v>
+        <v>0.2821</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>845.6</v>
+        <v>850</v>
       </c>
       <c r="D11" s="1">
-        <v>-6.8</v>
+        <v>-2.4</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.008</v>
+        <v>-0.0028</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-14.9</v>
+        <v>-10.5</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0173</v>
+        <v>-0.0122</v>
       </c>
       <c r="L11" s="1">
-        <v>-14.9</v>
+        <v>-10.5</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0173</v>
+        <v>-0.0122</v>
       </c>
       <c r="N11" s="1">
-        <v>-18.4</v>
+        <v>-14</v>
       </c>
       <c r="O11" s="1">
-        <v>-14.9</v>
+        <v>-10.5</v>
       </c>
       <c r="P11" s="1">
-        <v>-14.9</v>
+        <v>-10.5</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0288</v>
@@ -1330,28 +1330,28 @@
         <v>6</v>
       </c>
       <c r="T11" s="2">
-        <v>-0.008</v>
+        <v>-0.0028</v>
       </c>
       <c r="U11" s="5">
-        <v>2.114</v>
+        <v>2.125</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0175</v>
+        <v>0.0122</v>
       </c>
       <c r="X11" s="2">
-        <v>-0.0009</v>
+        <v>0.0043</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0302</v>
+        <v>0.0356</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.1699</v>
+        <v>0.176</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2599</v>
+        <v>0.2664</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29220.6</v>
+        <v>29351.5</v>
       </c>
       <c r="D12" s="1">
-        <v>-52.8</v>
+        <v>78.1</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-771.19</v>
+        <v>-640.29</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0257</v>
+        <v>-0.0213</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-181.1</v>
+        <v>-54.8</v>
       </c>
       <c r="O12" s="1">
-        <v>-771.19</v>
+        <v>-646.09</v>
       </c>
       <c r="P12" s="1">
-        <v>-771.19</v>
+        <v>-646.09</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9954</v>
